--- a/originales/respuestas/2025/01. Calificadas/bucle p12/Alcaldía Local De Engativá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p12/Alcaldía Local De Engativá.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Desktop\Respuesta\bucle p12\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unidades compartidas\VDLab\2025\2. Componente IIP\Etapa 3. Calificación\02. Calificadas\bucle p12\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990709A2-69B8-4423-8DC0-8F107B5D6D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2E6DED6-6EA9-4057-A26F-D31562F48DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{094CC916-D5EC-4887-8959-38C577BBB84C}"/>
   </bookViews>
